--- a/research/traditional_assets/database/data/mauritius/mauritius_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/mauritius/mauritius_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,43 +588,43 @@
         </is>
       </c>
       <c r="D2">
-        <v>1.065</v>
+        <v>1.547</v>
       </c>
       <c r="G2">
-        <v>0.1232951717272275</v>
+        <v>-0.009848484848484849</v>
       </c>
       <c r="H2">
-        <v>0.1232951717272275</v>
+        <v>-0.009848484848484849</v>
       </c>
       <c r="I2">
-        <v>-0.2349427575908412</v>
+        <v>0.112689393939394</v>
       </c>
       <c r="J2">
-        <v>-0.2349427575908412</v>
+        <v>0.112689393939394</v>
       </c>
       <c r="K2">
-        <v>-14.28</v>
+        <v>3.93</v>
       </c>
       <c r="L2">
-        <v>-0.3554006968641115</v>
+        <v>0.03721590909090909</v>
       </c>
       <c r="M2">
-        <v>0.7073999999999999</v>
+        <v>0.826</v>
       </c>
       <c r="N2">
-        <v>0.01165403624382207</v>
+        <v>0.01868778280542986</v>
       </c>
       <c r="O2">
-        <v>-0.04953781512605041</v>
+        <v>0.210178117048346</v>
       </c>
       <c r="P2">
-        <v>0.7073999999999999</v>
+        <v>0.826</v>
       </c>
       <c r="Q2">
-        <v>0.01165403624382207</v>
+        <v>0.01868778280542986</v>
       </c>
       <c r="R2">
-        <v>-0.04953781512605041</v>
+        <v>0.210178117048346</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,61 +633,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>0.01317957166392092</v>
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0.02874908558888076</v>
       </c>
       <c r="X2">
-        <v>0.04231896964162418</v>
+        <v>0.2856241161044373</v>
+      </c>
+      <c r="Y2">
+        <v>-0.2568750305155565</v>
       </c>
       <c r="Z2">
-        <v>3.105820514802504</v>
+        <v>0.271604938271605</v>
+      </c>
+      <c r="AA2">
+        <v>0.03060699588477367</v>
       </c>
       <c r="AB2">
-        <v>0.04226135509473829</v>
+        <v>0.09795921607287891</v>
+      </c>
+      <c r="AC2">
+        <v>-0.06735222018810524</v>
       </c>
       <c r="AD2">
-        <v>0.718</v>
+        <v>237.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.718</v>
+        <v>237.7</v>
       </c>
       <c r="AG2">
-        <v>-0.08200000000000007</v>
+        <v>237.7</v>
       </c>
       <c r="AH2">
-        <v>0.01169038392653619</v>
+        <v>0.8432068109258603</v>
       </c>
       <c r="AI2">
-        <v>0.04749305463685673</v>
+        <v>0.5212719298245614</v>
       </c>
       <c r="AJ2">
-        <v>-0.001352733511498236</v>
+        <v>0.8432068109258603</v>
       </c>
       <c r="AK2">
-        <v>-0.00572705685151558</v>
+        <v>0.5212719298245614</v>
       </c>
       <c r="AL2">
-        <v>14.018</v>
+        <v>13.4</v>
       </c>
       <c r="AM2">
-        <v>13.074</v>
+        <v>11.7</v>
       </c>
       <c r="AN2">
-        <v>0.2267845862286797</v>
+        <v>13.20555555555556</v>
       </c>
       <c r="AO2">
-        <v>-0.6734198887145099</v>
+        <v>0.8880597014925373</v>
       </c>
       <c r="AP2">
-        <v>-0.02590018951358183</v>
+        <v>13.20555555555556</v>
       </c>
       <c r="AQ2">
-        <v>-0.722043750956096</v>
+        <v>1.017094017094017</v>
       </c>
     </row>
     <row r="3">
@@ -698,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bravura Holdings Limited (NMSE:CMB)</t>
+          <t>BMH Ltd (MUSE:BMHL.N0000)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -706,223 +718,119 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D3">
+        <v>1.547</v>
+      </c>
       <c r="G3">
-        <v>-0.09204545454545454</v>
+        <v>-0.009848484848484849</v>
       </c>
       <c r="H3">
-        <v>-0.09204545454545454</v>
+        <v>-0.009848484848484849</v>
       </c>
       <c r="I3">
-        <v>0.1439393939393939</v>
+        <v>0.112689393939394</v>
       </c>
       <c r="J3">
-        <v>0.1439393939393939</v>
+        <v>0.112689393939394</v>
       </c>
       <c r="K3">
-        <v>-0.48</v>
+        <v>3.93</v>
       </c>
       <c r="L3">
-        <v>-0.0909090909090909</v>
+        <v>0.03721590909090909</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.826</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.01868778280542986</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.210178117048346</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.826</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.01868778280542986</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.210178117048346</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>0.04968944099378882</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>-0.03609022556390977</v>
+        <v>0.02874908558888076</v>
       </c>
       <c r="X3">
-        <v>0.04282526605379607</v>
+        <v>0.2856241161044373</v>
       </c>
       <c r="Y3">
-        <v>-0.07891549161770584</v>
+        <v>-0.2568750305155565</v>
       </c>
       <c r="Z3">
-        <v>0.4081317152353714</v>
+        <v>0.271604938271605</v>
       </c>
       <c r="AA3">
-        <v>0.05874623173842467</v>
+        <v>0.03060699588477367</v>
       </c>
       <c r="AB3">
-        <v>0.04271003696002428</v>
+        <v>0.09795921607287891</v>
       </c>
       <c r="AC3">
-        <v>0.0160361947784004</v>
+        <v>-0.06735222018810524</v>
       </c>
       <c r="AD3">
-        <v>0.718</v>
+        <v>237.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.718</v>
+        <v>237.7</v>
       </c>
       <c r="AG3">
-        <v>-0.08200000000000007</v>
+        <v>237.7</v>
       </c>
       <c r="AH3">
-        <v>0.04269235343084789</v>
+        <v>0.8432068109258603</v>
       </c>
       <c r="AI3">
-        <v>0.04749305463685673</v>
+        <v>0.5212719298245614</v>
       </c>
       <c r="AJ3">
-        <v>-0.005119240854039211</v>
+        <v>0.8432068109258603</v>
       </c>
       <c r="AK3">
-        <v>-0.00572705685151558</v>
+        <v>0.5212719298245614</v>
       </c>
       <c r="AL3">
-        <v>0.018</v>
+        <v>13.4</v>
       </c>
       <c r="AM3">
-        <v>-0.293</v>
+        <v>11.7</v>
       </c>
       <c r="AN3">
-        <v>0.9134860050890584</v>
+        <v>13.20555555555556</v>
       </c>
       <c r="AO3">
-        <v>42.22222222222223</v>
+        <v>0.8880597014925373</v>
       </c>
       <c r="AP3">
-        <v>-0.1043256997455472</v>
+        <v>13.20555555555556</v>
       </c>
       <c r="AQ3">
-        <v>-2.593856655290103</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Mauritius</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>BMH Ltd (MUSE:BMHL.N0000)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>1.065</v>
-      </c>
-      <c r="G4">
-        <v>0.1558739255014327</v>
-      </c>
-      <c r="H4">
-        <v>0.1558739255014327</v>
-      </c>
-      <c r="I4">
-        <v>-0.2922636103151862</v>
-      </c>
-      <c r="J4">
-        <v>-0.2922636103151862</v>
-      </c>
-      <c r="K4">
-        <v>-13.8</v>
-      </c>
-      <c r="L4">
-        <v>-0.3954154727793697</v>
-      </c>
-      <c r="M4">
-        <v>0.7073999999999999</v>
-      </c>
-      <c r="N4">
-        <v>0.0158609865470852</v>
-      </c>
-      <c r="O4">
-        <v>-0.05126086956521738</v>
-      </c>
-      <c r="P4">
-        <v>0.7073999999999999</v>
-      </c>
-      <c r="Q4">
-        <v>0.0158609865470852</v>
-      </c>
-      <c r="R4">
-        <v>-0.05126086956521738</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>0.0418126732294523</v>
-      </c>
-      <c r="AB4">
-        <v>0.0418126732294523</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>0</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>0</v>
-      </c>
-      <c r="AL4">
-        <v>14</v>
-      </c>
-      <c r="AM4">
-        <v>13.367</v>
-      </c>
-      <c r="AN4">
-        <v>0</v>
-      </c>
-      <c r="AO4">
-        <v>-0.7285714285714285</v>
-      </c>
-      <c r="AP4">
-        <v>0</v>
-      </c>
-      <c r="AQ4">
-        <v>-0.7630732400688262</v>
+        <v>1.017094017094017</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/mauritius/mauritius_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/mauritius/mauritius_brokerage_investment_banking.xlsx
@@ -588,43 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>1.547</v>
+        <v>1.45</v>
+      </c>
+      <c r="E2">
+        <v>-0.0411</v>
       </c>
       <c r="G2">
-        <v>-0.009848484848484849</v>
+        <v>0.203001579778831</v>
       </c>
       <c r="H2">
-        <v>-0.009848484848484849</v>
+        <v>0.203001579778831</v>
       </c>
       <c r="I2">
-        <v>0.112689393939394</v>
+        <v>0.1642969984202212</v>
       </c>
       <c r="J2">
-        <v>0.112689393939394</v>
+        <v>0.121843613426967</v>
       </c>
       <c r="K2">
-        <v>3.93</v>
+        <v>4.98</v>
       </c>
       <c r="L2">
-        <v>0.03721590909090909</v>
+        <v>0.03933649289099526</v>
       </c>
       <c r="M2">
-        <v>0.826</v>
+        <v>0.795</v>
       </c>
       <c r="N2">
-        <v>0.01868778280542986</v>
+        <v>0.01929611650485437</v>
       </c>
       <c r="O2">
-        <v>0.210178117048346</v>
+        <v>0.1596385542168675</v>
       </c>
       <c r="P2">
-        <v>0.826</v>
+        <v>0.795</v>
       </c>
       <c r="Q2">
-        <v>0.01868778280542986</v>
+        <v>0.01929611650485437</v>
       </c>
       <c r="R2">
-        <v>0.210178117048346</v>
+        <v>0.1596385542168675</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>0.2233009708737864</v>
       </c>
       <c r="W2">
-        <v>0.02874908558888076</v>
+        <v>0.03747178329571106</v>
       </c>
       <c r="X2">
-        <v>0.2856241161044373</v>
+        <v>0.1872020480279748</v>
       </c>
       <c r="Y2">
-        <v>-0.2568750305155565</v>
+        <v>-0.1497302647322637</v>
       </c>
       <c r="Z2">
-        <v>0.271604938271605</v>
+        <v>0.3736717827626918</v>
       </c>
       <c r="AA2">
-        <v>0.03060699588477367</v>
+        <v>0.04552952024750299</v>
       </c>
       <c r="AB2">
-        <v>0.09795921607287891</v>
+        <v>0.08753913170742843</v>
       </c>
       <c r="AC2">
-        <v>-0.06735222018810524</v>
+        <v>-0.04200961145992543</v>
       </c>
       <c r="AD2">
-        <v>237.7</v>
+        <v>189.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>237.7</v>
+        <v>189.3</v>
       </c>
       <c r="AG2">
-        <v>237.7</v>
+        <v>180.1</v>
       </c>
       <c r="AH2">
-        <v>0.8432068109258603</v>
+        <v>0.8212581344902387</v>
       </c>
       <c r="AI2">
-        <v>0.5212719298245614</v>
+        <v>0.4299341358164888</v>
       </c>
       <c r="AJ2">
-        <v>0.8432068109258603</v>
+        <v>0.8138273836421148</v>
       </c>
       <c r="AK2">
-        <v>0.5212719298245614</v>
+        <v>0.4177684991881234</v>
       </c>
       <c r="AL2">
-        <v>13.4</v>
+        <v>16.1</v>
       </c>
       <c r="AM2">
-        <v>11.7</v>
+        <v>14.42</v>
       </c>
       <c r="AN2">
-        <v>13.20555555555556</v>
+        <v>6.247524752475248</v>
       </c>
       <c r="AO2">
-        <v>0.8880597014925373</v>
+        <v>1.291925465838509</v>
       </c>
       <c r="AP2">
-        <v>13.20555555555556</v>
+        <v>5.943894389438944</v>
       </c>
       <c r="AQ2">
-        <v>1.017094017094017</v>
+        <v>1.442441054091539</v>
       </c>
     </row>
     <row r="3">
@@ -719,43 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>1.547</v>
+        <v>1.45</v>
+      </c>
+      <c r="E3">
+        <v>-0.0411</v>
       </c>
       <c r="G3">
-        <v>-0.009848484848484849</v>
+        <v>0.203001579778831</v>
       </c>
       <c r="H3">
-        <v>-0.009848484848484849</v>
+        <v>0.203001579778831</v>
       </c>
       <c r="I3">
-        <v>0.112689393939394</v>
+        <v>0.1642969984202212</v>
       </c>
       <c r="J3">
-        <v>0.112689393939394</v>
+        <v>0.121843613426967</v>
       </c>
       <c r="K3">
-        <v>3.93</v>
+        <v>4.98</v>
       </c>
       <c r="L3">
-        <v>0.03721590909090909</v>
+        <v>0.03933649289099526</v>
       </c>
       <c r="M3">
-        <v>0.826</v>
+        <v>0.795</v>
       </c>
       <c r="N3">
-        <v>0.01868778280542986</v>
+        <v>0.01929611650485437</v>
       </c>
       <c r="O3">
-        <v>0.210178117048346</v>
+        <v>0.1596385542168675</v>
       </c>
       <c r="P3">
-        <v>0.826</v>
+        <v>0.795</v>
       </c>
       <c r="Q3">
-        <v>0.01868778280542986</v>
+        <v>0.01929611650485437</v>
       </c>
       <c r="R3">
-        <v>0.210178117048346</v>
+        <v>0.1596385542168675</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.2233009708737864</v>
       </c>
       <c r="W3">
-        <v>0.02874908558888076</v>
+        <v>0.03747178329571106</v>
       </c>
       <c r="X3">
-        <v>0.2856241161044373</v>
+        <v>0.1872020480279748</v>
       </c>
       <c r="Y3">
-        <v>-0.2568750305155565</v>
+        <v>-0.1497302647322637</v>
       </c>
       <c r="Z3">
-        <v>0.271604938271605</v>
+        <v>0.3736717827626918</v>
       </c>
       <c r="AA3">
-        <v>0.03060699588477367</v>
+        <v>0.04552952024750299</v>
       </c>
       <c r="AB3">
-        <v>0.09795921607287891</v>
+        <v>0.08753913170742843</v>
       </c>
       <c r="AC3">
-        <v>-0.06735222018810524</v>
+        <v>-0.04200961145992543</v>
       </c>
       <c r="AD3">
-        <v>237.7</v>
+        <v>189.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>237.7</v>
+        <v>189.3</v>
       </c>
       <c r="AG3">
-        <v>237.7</v>
+        <v>180.1</v>
       </c>
       <c r="AH3">
-        <v>0.8432068109258603</v>
+        <v>0.8212581344902387</v>
       </c>
       <c r="AI3">
-        <v>0.5212719298245614</v>
+        <v>0.4299341358164888</v>
       </c>
       <c r="AJ3">
-        <v>0.8432068109258603</v>
+        <v>0.8138273836421148</v>
       </c>
       <c r="AK3">
-        <v>0.5212719298245614</v>
+        <v>0.4177684991881234</v>
       </c>
       <c r="AL3">
-        <v>13.4</v>
+        <v>16.1</v>
       </c>
       <c r="AM3">
-        <v>11.7</v>
+        <v>14.42</v>
       </c>
       <c r="AN3">
-        <v>13.20555555555556</v>
+        <v>6.247524752475248</v>
       </c>
       <c r="AO3">
-        <v>0.8880597014925373</v>
+        <v>1.291925465838509</v>
       </c>
       <c r="AP3">
-        <v>13.20555555555556</v>
+        <v>5.943894389438944</v>
       </c>
       <c r="AQ3">
-        <v>1.017094017094017</v>
+        <v>1.442441054091539</v>
       </c>
     </row>
   </sheetData>
